--- a/Final Outputs/Mahjong_x_Block_Beatchart.xlsx
+++ b/Final Outputs/Mahjong_x_Block_Beatchart.xlsx
@@ -1,28 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5C238898EB2A7B387839CF531EB73B3F83B225C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
-    <sheet name="Đường cong độ khó" sheetId="1" r:id="rId1"/>
-    <sheet name="Level Difficulty" sheetId="2" r:id="rId2"/>
-    <sheet name="Công thức" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Đường cong độ khó" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Level Difficulty" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Công thức" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Economy" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="111">
   <si>
     <t>Màn</t>
   </si>
@@ -42,6 +37,12 @@
     <t>Nước lời giải</t>
   </si>
   <si>
+    <t>Nước thắng thật</t>
+  </si>
+  <si>
+    <t>Nước chết sau thắng</t>
+  </si>
+  <si>
     <t>Lượt dư</t>
   </si>
   <si>
@@ -202,33 +203,187 @@
   </si>
   <si>
     <t>Lưu ý (11/09/2026, đổi thứ tự dạy cơ chế theo yêu cầu người dùng): Chương 2 (Ô Chắn, TB 40.6) hiện có điểm trung bình CAO HƠN Chương 3 (Phong Ấn, TB 33.5), phá vỡ quy tắc "độ khó tăng dần theo chương" ở §2 của 08-GDD-LEVEL-DESIGN.md. Đây là đánh đổi CÓ CHỦ Ý: ưu tiên thứ tự dạy cơ chế (Ô Chắn dễ hiểu hơn nên dạy trước, Phong Ấn phức tạp hơn nên dạy sau) hơn đường cong độ khó tuyệt đối theo chương. Cần 1 đợt cân bằng lại riêng nếu muốn khôi phục tính đơn điệu.</t>
+  </si>
+  <si>
+    <t>Xu theo màn (computeWinCoins() — chỉ tính Xu kiếm được, không tính giá shop)</t>
+  </si>
+  <si>
+    <t>Lượt dư tại điểm thắng</t>
+  </si>
+  <si>
+    <t>Xu Sàn</t>
+  </si>
+  <si>
+    <t>Xu +Lượt dư (tối đa)</t>
+  </si>
+  <si>
+    <t>Xu +Không dùng Booster</t>
+  </si>
+  <si>
+    <t>Nhân đôi cuối chương?</t>
+  </si>
+  <si>
+    <t>Xu Tối Đa (chơi tốt nhất)</t>
+  </si>
+  <si>
+    <t>Xu Tệ Nhất (dùng hết booster, 0 lượt dư)</t>
+  </si>
+  <si>
+    <t>Cộng dồn Tối Đa</t>
+  </si>
+  <si>
+    <t>Cộng dồn Tệ Nhất</t>
+  </si>
+  <si>
+    <t>Có (×2)</t>
+  </si>
+  <si>
+    <t>Ghi chú công thức (computeWinCoins(), index.html)</t>
+  </si>
+  <si>
+    <t>= round(10 × ln(màn + 2)) — màn 1-indexed; tăng nhanh đầu game, chạm ~40 Xu ở Lv50.</t>
+  </si>
+  <si>
+    <t>Xu +Lượt dư</t>
+  </si>
+  <si>
+    <t>= max(0, Move Limit − Nước thắng thật) × 2 Xu/lượt — dùng NƯỚC THẮNG THẬT (levelWon() check ngay sau mọi nước), không phải toàn bộ Nước lời giải — chơi càng nhanh, dư càng nhiều, Xu bonus càng cao.</t>
+  </si>
+  <si>
+    <t>= +15 Xu cố định nếu hết màn mà không dùng mất Booster nào (Đổi khối/Hint) so với lúc bắt đầu màn.</t>
+  </si>
+  <si>
+    <t>Nhân đôi cuối chương</t>
+  </si>
+  <si>
+    <t>×2 TOÀN BỘ tổng Xu (Sàn + Lượt dư + Không Booster) ở đúng màn thứ 10, 20, 30, 40, 50.</t>
+  </si>
+  <si>
+    <t>Xu Tệ Nhất</t>
+  </si>
+  <si>
+    <t>Kịch bản người chơi luôn dùng hết Booster + luôn hết đúng lượt (0 dư) — vẫn được Xu Sàn (và ×2 nếu là màn cuối chương). Validate: cộng dồn tới Lv30 = 899 Xu, khớp đúng giá skin rẻ nhất (895 Xu, xem GAME_DESIGN_DOCUMENT.md mục 7.1).</t>
+  </si>
+  <si>
+    <t>Chơi lại màn đã qua</t>
+  </si>
+  <si>
+    <t>firstClear=false → LUÔN 0 Xu bất kể kịch bản nào ở trên (không lặp lại để cày Xu).</t>
+  </si>
+  <si>
+    <t>Nguồn Booster (Đổi khối / Hint) — KHÔNG theo từng màn</t>
+  </si>
+  <si>
+    <t>[Quan trọng] Booster đọc từ 1 KHO DÙNG CHUNG toàn game (localStorage mxb_booster_reroll/mxb_booster_hint), không cấp riêng theo từng level nữa (xem index.html dòng ~7372: "Booster giờ đọc từ kho DÙNG CHUNG toàn game"). Các cột "Đổi khối"/"Hint" trong sheet "Level Difficulty" là field level.boosterReroll/level.boosterHint CÒN SÓT LẠI trong dữ liệu màn từ thiết kế cũ (cấp booster riêng mỗi màn) — ENGINE HIỆN TẠI KHÔNG ĐỌC 2 field này nữa, giữ nguyên trong data chỉ vì chưa dọn, không phản ánh Xu/booster thật người chơi nhận được.</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>Điều kiện</t>
+  </si>
+  <si>
+    <t>Thưởng Booster</t>
+  </si>
+  <si>
+    <t>Nhiệm vụ hàng ngày — "Dùng 1 lượt Đổi khối hoặc Hint"</t>
+  </si>
+  <si>
+    <t>1 lần/ngày</t>
+  </si>
+  <si>
+    <t>+1 Đổi khối, +1 Hint</t>
+  </si>
+  <si>
+    <t>Nhiệm vụ hàng ngày — mốc hoàn thành 2/3 nhiệm vụ</t>
+  </si>
+  <si>
+    <t>Hoàn thành đúng 2 trong 3 nhiệm vụ được chọn hôm nay</t>
+  </si>
+  <si>
+    <t>+1 Đổi khối</t>
+  </si>
+  <si>
+    <t>Nhiệm vụ hàng ngày — mốc hoàn thành cả 3/3</t>
+  </si>
+  <si>
+    <t>Hoàn thành cả 3 nhiệm vụ được chọn hôm nay</t>
+  </si>
+  <si>
+    <t>Điểm danh 30 ngày — ngày chia hết cho 5 (trừ mốc lớn)</t>
+  </si>
+  <si>
+    <t>Thắng ≥1 màn hôm đó</t>
+  </si>
+  <si>
+    <t>Điểm danh 30 ngày — Ngày 10</t>
+  </si>
+  <si>
+    <t>+3 Đổi khối, +3 Hint</t>
+  </si>
+  <si>
+    <t>Điểm danh 30 ngày — Ngày 20</t>
+  </si>
+  <si>
+    <t>+5 Đổi khối, +5 Hint</t>
+  </si>
+  <si>
+    <t>Điểm danh 30 ngày — Ngày 30</t>
+  </si>
+  <si>
+    <t>+8 Đổi khối, +8 Hint</t>
+  </si>
+  <si>
+    <t>Cửa hàng — mua gói Booster</t>
+  </si>
+  <si>
+    <t>100 Xu/gói (Đổi khối HOẶC Hint)</t>
+  </si>
+  <si>
+    <t>+5 Đổi khối HOẶC +5 Hint (chọn 1 loại/lần mua)</t>
+  </si>
+  <si>
+    <t>Khởi tạo lần đầu</t>
+  </si>
+  <si>
+    <t>Người chơi mới, chưa từng nhận gì</t>
+  </si>
+  <si>
+    <t>5 Đổi khối, 5 Hint (mặc định trong kho dùng chung)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -301,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -328,6 +483,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -347,7 +504,7 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>4000</xdr:colOff>
@@ -357,7 +514,7 @@
     <xdr:ext cx="9525000" cy="3543300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="1" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -710,45 +867,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z51"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -756,23 +913,23 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="7" customWidth="1"/>
-    <col min="12" max="12" width="6" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="9" style="1" customWidth="1"/>
     <col min="19" max="19" width="10" style="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10" style="1" customWidth="1"/>
     <col min="22" max="22" width="9" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="1" customWidth="1"/>
+    <col min="25" max="25" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -791,10 +948,10 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -818,10 +975,10 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
@@ -842,22 +999,28 @@
       <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -868,70 +1031,76 @@
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
       </c>
       <c r="O2">
         <v>2</v>
       </c>
-      <c r="P2" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
+        <v>2</v>
+      </c>
+      <c r="T2" s="1">
         <v>1.5</v>
       </c>
-      <c r="S2" s="1">
+      <c r="U2" s="1">
         <v>2.4</v>
-      </c>
-      <c r="T2" s="1">
-        <v>0</v>
-      </c>
-      <c r="U2" s="1">
-        <v>1</v>
       </c>
       <c r="V2" s="1">
         <v>0</v>
       </c>
       <c r="W2" s="1">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
         <v>7.9</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -940,72 +1109,78 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3">
         <v>5</v>
       </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="1">
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="1">
         <v>2.25</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="S3" s="1">
         <v>5</v>
       </c>
-      <c r="R3" s="1">
+      <c r="T3" s="1">
         <v>3</v>
       </c>
-      <c r="S3" s="1">
-        <v>6</v>
-      </c>
-      <c r="T3" s="1">
-        <v>0</v>
-      </c>
       <c r="U3" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V3" s="1">
         <v>0</v>
       </c>
       <c r="W3" s="1">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
         <v>17.3</v>
       </c>
-      <c r="X3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1014,72 +1189,78 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>6</v>
-      </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="1">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4">
+        <v>6</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="1">
         <v>4</v>
       </c>
-      <c r="Q4" s="1">
-        <v>6</v>
-      </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
+        <v>6</v>
+      </c>
+      <c r="T4" s="1">
         <v>3</v>
       </c>
-      <c r="S4" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T4" s="1">
-        <v>0</v>
-      </c>
       <c r="U4" s="1">
-        <v>1</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="V4" s="1">
         <v>0</v>
       </c>
       <c r="W4" s="1">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
         <v>21.2</v>
       </c>
-      <c r="X4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -1088,72 +1269,78 @@
         <v>7</v>
       </c>
       <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
-      </c>
-      <c r="N5">
-        <v>2</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="1">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="1">
         <v>4</v>
       </c>
-      <c r="Q5" s="1">
-        <v>7</v>
-      </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
+        <v>7</v>
+      </c>
+      <c r="T5" s="1">
         <v>4.5</v>
       </c>
-      <c r="S5" s="1">
+      <c r="U5" s="1">
         <v>9.6</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-      <c r="U5" s="1">
-        <v>1</v>
       </c>
       <c r="V5" s="1">
         <v>0</v>
       </c>
       <c r="W5" s="1">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
         <v>26.1</v>
       </c>
-      <c r="X5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1162,72 +1349,78 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-      <c r="N6">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
         <v>3</v>
       </c>
-      <c r="O6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="1">
+      <c r="Q6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="1">
         <v>4</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="S6" s="1">
         <v>4</v>
       </c>
-      <c r="R6" s="1">
+      <c r="T6" s="1">
         <v>1.5</v>
       </c>
-      <c r="S6" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
       <c r="U6" s="1">
-        <v>1.5</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
         <v>18.2</v>
       </c>
-      <c r="X6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -1236,72 +1429,78 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
-      </c>
-      <c r="N7">
-        <v>2</v>
-      </c>
-      <c r="O7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="1">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7">
+        <v>6</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="1">
         <v>4</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="S7" s="1">
         <v>5</v>
       </c>
-      <c r="R7" s="1">
+      <c r="T7" s="1">
         <v>1.5</v>
       </c>
-      <c r="S7" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1">
-        <v>1</v>
-      </c>
-      <c r="V7" s="1">
-        <v>2</v>
-      </c>
       <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="1">
         <v>20.7</v>
       </c>
-      <c r="X7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -1310,72 +1509,78 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8">
         <v>5</v>
       </c>
-      <c r="N8">
-        <v>2</v>
-      </c>
-      <c r="O8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="1">
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="1">
         <v>9</v>
       </c>
-      <c r="Q8" s="1">
-        <v>6</v>
-      </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
+        <v>6</v>
+      </c>
+      <c r="T8" s="1">
         <v>1.5</v>
       </c>
-      <c r="S8" s="1">
-        <v>6</v>
-      </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
+        <v>6</v>
+      </c>
+      <c r="V8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="1">
-        <v>1</v>
-      </c>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
       <c r="W8" s="1">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="1">
         <v>25.5</v>
       </c>
-      <c r="X8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1390,66 +1595,72 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>6</v>
-      </c>
-      <c r="N9">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
         <v>3</v>
       </c>
-      <c r="O9" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="1">
+      <c r="Q9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="S9" s="1">
         <v>3</v>
       </c>
-      <c r="R9" s="1">
+      <c r="T9" s="1">
         <v>1.5</v>
       </c>
-      <c r="S9" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="1">
+      <c r="W9" s="1">
         <v>1.5</v>
       </c>
-      <c r="V9" s="1">
-        <v>2</v>
-      </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="1">
         <v>21.5</v>
       </c>
-      <c r="X9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1458,72 +1669,78 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
       </c>
       <c r="N10">
-        <v>2</v>
-      </c>
-      <c r="O10" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>6</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="S10" s="1">
         <v>5</v>
       </c>
-      <c r="R10" s="1">
+      <c r="T10" s="1">
         <v>1.5</v>
       </c>
-      <c r="S10" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V10" s="1">
         <v>3</v>
       </c>
-      <c r="U10" s="1">
-        <v>1</v>
-      </c>
-      <c r="V10" s="1">
-        <v>2</v>
-      </c>
       <c r="W10" s="1">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="1">
         <v>26</v>
       </c>
-      <c r="X10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="E11" s="5">
         <v>9</v>
@@ -1531,73 +1748,79 @@
       <c r="F11" s="5">
         <v>7</v>
       </c>
-      <c r="G11" s="5">
-        <v>2</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>1</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="5">
-        <v>7</v>
-      </c>
-      <c r="N11" s="5">
+        <v>29</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="5">
+        <v>7</v>
+      </c>
+      <c r="P11" s="5">
         <v>3</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="Q11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="7">
         <v>6.25</v>
       </c>
-      <c r="Q11" s="7">
-        <v>7</v>
-      </c>
-      <c r="R11" s="7">
+      <c r="S11" s="7">
+        <v>7</v>
+      </c>
+      <c r="T11" s="7">
         <v>1.5</v>
       </c>
-      <c r="S11" s="7">
+      <c r="U11" s="7">
         <v>8.4</v>
       </c>
-      <c r="T11" s="7">
+      <c r="V11" s="7">
         <v>0</v>
       </c>
-      <c r="U11" s="7">
+      <c r="W11" s="7">
         <v>1.5</v>
       </c>
-      <c r="V11" s="7">
-        <v>2</v>
-      </c>
-      <c r="W11" s="7">
+      <c r="X11" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="7">
         <v>26.7</v>
       </c>
-      <c r="X11" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1606,73 +1829,79 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12">
         <v>3</v>
       </c>
-      <c r="L12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12">
-        <v>7</v>
-      </c>
-      <c r="N12">
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
+      <c r="P12">
         <v>3</v>
       </c>
-      <c r="O12" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="1">
+      <c r="Q12" t="s">
+        <v>29</v>
+      </c>
+      <c r="R12" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q12" s="1">
-        <v>8</v>
-      </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
+        <v>8</v>
+      </c>
+      <c r="T12" s="1">
         <v>3</v>
       </c>
-      <c r="S12" s="1">
+      <c r="U12" s="1">
         <v>8.4</v>
       </c>
-      <c r="T12" s="1">
-        <v>6</v>
-      </c>
-      <c r="U12" s="1">
+      <c r="V12" s="1">
+        <v>6</v>
+      </c>
+      <c r="W12" s="1">
         <v>1.5</v>
       </c>
-      <c r="V12" s="1">
-        <v>2</v>
-      </c>
-      <c r="W12" s="1">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="X12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X12" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>35.2</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>33</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
       <c r="E13">
         <v>7</v>
       </c>
@@ -1680,73 +1909,79 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N13">
-        <v>2</v>
-      </c>
-      <c r="O13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>6</v>
+      </c>
+      <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q13" s="1">
-        <v>6</v>
-      </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
+        <v>6</v>
+      </c>
+      <c r="T13" s="1">
         <v>3</v>
       </c>
-      <c r="S13" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T13" s="1">
-        <v>7</v>
-      </c>
       <c r="U13" s="1">
-        <v>1</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="V13" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W13" s="1">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="1">
         <v>32.5</v>
       </c>
-      <c r="X13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
       <c r="E14">
         <v>8</v>
       </c>
@@ -1754,72 +1989,78 @@
         <v>7</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14">
         <v>3</v>
       </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14">
-        <v>7</v>
-      </c>
-      <c r="N14">
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14">
+        <v>7</v>
+      </c>
+      <c r="P14">
         <v>3</v>
       </c>
-      <c r="O14" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="1">
+      <c r="Q14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R14" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q14" s="1">
-        <v>7</v>
-      </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
+        <v>7</v>
+      </c>
+      <c r="T14" s="1">
         <v>3</v>
       </c>
-      <c r="S14" s="1">
+      <c r="U14" s="1">
         <v>8.4</v>
       </c>
-      <c r="T14" s="1">
-        <v>6</v>
-      </c>
-      <c r="U14" s="1">
+      <c r="V14" s="1">
+        <v>6</v>
+      </c>
+      <c r="W14" s="1">
         <v>1.5</v>
       </c>
-      <c r="V14" s="1">
-        <v>2</v>
-      </c>
-      <c r="W14" s="1">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="X14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X14" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>34.2</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1828,72 +2069,78 @@
         <v>8</v>
       </c>
       <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15">
         <v>4</v>
       </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15">
-        <v>7</v>
-      </c>
-      <c r="N15">
+      <c r="N15" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15">
+        <v>7</v>
+      </c>
+      <c r="P15">
         <v>3</v>
       </c>
-      <c r="O15" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="1">
+      <c r="Q15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="1">
         <v>9</v>
       </c>
-      <c r="Q15" s="1">
-        <v>8</v>
-      </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
+        <v>8</v>
+      </c>
+      <c r="T15" s="1">
         <v>3</v>
       </c>
-      <c r="S15" s="1">
+      <c r="U15" s="1">
         <v>8.4</v>
       </c>
-      <c r="T15" s="1">
-        <v>8</v>
-      </c>
-      <c r="U15" s="1">
+      <c r="V15" s="1">
+        <v>8</v>
+      </c>
+      <c r="W15" s="1">
         <v>1.5</v>
       </c>
-      <c r="V15" s="1">
-        <v>2</v>
-      </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="1">
         <v>39.9</v>
       </c>
-      <c r="X15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -1902,72 +2149,78 @@
         <v>7</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16">
         <v>5</v>
       </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16">
-        <v>7</v>
-      </c>
-      <c r="N16">
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16">
+        <v>7</v>
+      </c>
+      <c r="P16">
         <v>3</v>
       </c>
-      <c r="O16" t="s">
-        <v>27</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="Q16" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="1">
         <v>9</v>
       </c>
-      <c r="Q16" s="1">
-        <v>7</v>
-      </c>
-      <c r="R16" s="1">
+      <c r="S16" s="1">
+        <v>7</v>
+      </c>
+      <c r="T16" s="1">
         <v>3</v>
       </c>
-      <c r="S16" s="1">
+      <c r="U16" s="1">
         <v>8.4</v>
       </c>
-      <c r="T16" s="1">
+      <c r="V16" s="1">
         <v>10</v>
       </c>
-      <c r="U16" s="1">
+      <c r="W16" s="1">
         <v>1.5</v>
       </c>
-      <c r="V16" s="1">
-        <v>2</v>
-      </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="1">
         <v>40.9</v>
       </c>
-      <c r="X16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1976,72 +2229,78 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17">
         <v>4</v>
       </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17">
-        <v>7</v>
-      </c>
-      <c r="N17">
+      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17">
+        <v>7</v>
+      </c>
+      <c r="P17">
         <v>3</v>
       </c>
-      <c r="O17" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17" s="1">
+      <c r="Q17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R17" s="1">
         <v>9</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="S17" s="1">
         <v>9</v>
       </c>
-      <c r="R17" s="1">
+      <c r="T17" s="1">
         <v>3</v>
       </c>
-      <c r="S17" s="1">
+      <c r="U17" s="1">
         <v>8.4</v>
       </c>
-      <c r="T17" s="1">
-        <v>8</v>
-      </c>
-      <c r="U17" s="1">
+      <c r="V17" s="1">
+        <v>8</v>
+      </c>
+      <c r="W17" s="1">
         <v>1.5</v>
       </c>
-      <c r="V17" s="1">
-        <v>2</v>
-      </c>
-      <c r="W17" s="1">
+      <c r="X17" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="1">
         <v>40.9</v>
       </c>
-      <c r="X17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18">
         <v>9</v>
@@ -2050,72 +2309,78 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M18">
-        <v>7</v>
-      </c>
-      <c r="N18">
+        <v>6</v>
+      </c>
+      <c r="N18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18">
+        <v>7</v>
+      </c>
+      <c r="P18">
         <v>3</v>
       </c>
-      <c r="O18" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="Q18" t="s">
+        <v>29</v>
+      </c>
+      <c r="R18" s="1">
         <v>9</v>
       </c>
-      <c r="Q18" s="1">
-        <v>8</v>
-      </c>
-      <c r="R18" s="1">
+      <c r="S18" s="1">
+        <v>8</v>
+      </c>
+      <c r="T18" s="1">
         <v>3</v>
       </c>
-      <c r="S18" s="1">
+      <c r="U18" s="1">
         <v>8.4</v>
       </c>
-      <c r="T18" s="1">
+      <c r="V18" s="1">
         <v>12</v>
       </c>
-      <c r="U18" s="1">
+      <c r="W18" s="1">
         <v>1.5</v>
       </c>
-      <c r="V18" s="1">
+      <c r="X18" s="1">
         <v>4</v>
       </c>
-      <c r="W18" s="1">
+      <c r="Y18" s="1">
         <v>45.9</v>
       </c>
-      <c r="X18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19">
         <v>8</v>
@@ -2124,72 +2389,78 @@
         <v>8</v>
       </c>
       <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19">
         <v>3</v>
       </c>
-      <c r="L19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19">
-        <v>7</v>
-      </c>
-      <c r="N19">
+      <c r="N19" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19">
+        <v>7</v>
+      </c>
+      <c r="P19">
         <v>3</v>
       </c>
-      <c r="O19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="Q19" t="s">
+        <v>29</v>
+      </c>
+      <c r="R19" s="1">
         <v>9</v>
       </c>
-      <c r="Q19" s="1">
-        <v>8</v>
-      </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
+        <v>8</v>
+      </c>
+      <c r="T19" s="1">
         <v>4.5</v>
       </c>
-      <c r="S19" s="1">
+      <c r="U19" s="1">
         <v>8.4</v>
       </c>
-      <c r="T19" s="1">
-        <v>6</v>
-      </c>
-      <c r="U19" s="1">
+      <c r="V19" s="1">
+        <v>6</v>
+      </c>
+      <c r="W19" s="1">
         <v>1.5</v>
       </c>
-      <c r="V19" s="1">
-        <v>2</v>
-      </c>
-      <c r="W19" s="1">
+      <c r="X19" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="1">
         <v>39.4</v>
       </c>
-      <c r="X19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2198,72 +2469,78 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M20">
         <v>8</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>8</v>
+      </c>
+      <c r="P20">
         <v>3</v>
       </c>
-      <c r="O20" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="1">
+      <c r="Q20" t="s">
+        <v>29</v>
+      </c>
+      <c r="R20" s="1">
         <v>9</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="S20" s="1">
         <v>9</v>
       </c>
-      <c r="R20" s="1">
+      <c r="T20" s="1">
         <v>3</v>
       </c>
-      <c r="S20" s="1">
+      <c r="U20" s="1">
         <v>9.6</v>
       </c>
-      <c r="T20" s="1">
+      <c r="V20" s="1">
         <v>16</v>
       </c>
-      <c r="U20" s="1">
+      <c r="W20" s="1">
         <v>1.5</v>
       </c>
-      <c r="V20" s="1">
-        <v>2</v>
-      </c>
-      <c r="W20" s="1">
+      <c r="X20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="1">
         <v>50.1</v>
       </c>
-      <c r="X20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="5">
         <v>11</v>
@@ -2271,73 +2548,79 @@
       <c r="F21" s="5">
         <v>8</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21">
+        <v>6</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5">
         <v>3</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="5">
-        <v>1</v>
-      </c>
       <c r="J21" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K21" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M21" s="5">
-        <v>7</v>
-      </c>
-      <c r="N21" s="5">
+        <v>8</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="5">
+        <v>7</v>
+      </c>
+      <c r="P21" s="5">
         <v>3</v>
       </c>
-      <c r="O21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="7">
+      <c r="Q21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R21" s="7">
         <v>9</v>
       </c>
-      <c r="Q21" s="7">
-        <v>8</v>
-      </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
+        <v>8</v>
+      </c>
+      <c r="T21" s="7">
         <v>0</v>
       </c>
-      <c r="S21" s="7">
+      <c r="U21" s="7">
         <v>8.4</v>
       </c>
-      <c r="T21" s="7">
+      <c r="V21" s="7">
         <v>16</v>
       </c>
-      <c r="U21" s="7">
+      <c r="W21" s="7">
         <v>1.5</v>
       </c>
-      <c r="V21" s="7">
+      <c r="X21" s="7">
         <v>4</v>
       </c>
-      <c r="W21" s="7">
+      <c r="Y21" s="7">
         <v>46.9</v>
       </c>
-      <c r="X21" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z21" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2346,72 +2629,78 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="K22" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22">
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22">
         <v>5</v>
       </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="P22">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>29</v>
+      </c>
+      <c r="R22" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="S22" s="1">
         <v>5</v>
       </c>
-      <c r="R22" s="1">
+      <c r="T22" s="1">
         <v>1.5</v>
       </c>
-      <c r="S22" s="1">
-        <v>6</v>
-      </c>
-      <c r="T22" s="1">
-        <v>2</v>
-      </c>
       <c r="U22" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="1">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="1">
         <v>22.8</v>
       </c>
-      <c r="X22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E23">
         <v>11</v>
@@ -2420,72 +2709,78 @@
         <v>11</v>
       </c>
       <c r="G23">
+        <v>11</v>
+      </c>
+      <c r="H23">
         <v>0</v>
       </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
-      </c>
-      <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23">
-        <v>7</v>
-      </c>
-      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23">
+        <v>7</v>
+      </c>
+      <c r="P23">
         <v>3</v>
       </c>
-      <c r="O23" t="s">
-        <v>27</v>
-      </c>
-      <c r="P23" s="1">
+      <c r="Q23" t="s">
+        <v>29</v>
+      </c>
+      <c r="R23" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="S23" s="1">
         <v>11</v>
       </c>
-      <c r="R23" s="1">
+      <c r="T23" s="1">
         <v>4.5</v>
       </c>
-      <c r="S23" s="1">
+      <c r="U23" s="1">
         <v>8.4</v>
       </c>
-      <c r="T23" s="1">
+      <c r="V23" s="1">
         <v>4</v>
       </c>
-      <c r="U23" s="1">
+      <c r="W23" s="1">
         <v>1.5</v>
       </c>
-      <c r="V23" s="1">
-        <v>1</v>
-      </c>
-      <c r="W23" s="1">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="X23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X23" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s">
         <v>33</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
       </c>
       <c r="E24">
         <v>11</v>
@@ -2494,73 +2789,79 @@
         <v>11</v>
       </c>
       <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>6</v>
+      </c>
+      <c r="I24">
         <v>0</v>
       </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
       <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
         <v>4</v>
       </c>
-      <c r="K24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24">
+      <c r="M24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24">
         <v>10</v>
       </c>
-      <c r="N24">
-        <v>2</v>
-      </c>
-      <c r="O24" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="1">
+      <c r="P24">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>29</v>
+      </c>
+      <c r="R24" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="S24" s="1">
         <v>11</v>
       </c>
-      <c r="R24" s="1">
+      <c r="T24" s="1">
         <v>4.5</v>
       </c>
-      <c r="S24" s="1">
+      <c r="U24" s="1">
         <v>12</v>
       </c>
-      <c r="T24" s="1">
-        <v>8</v>
-      </c>
-      <c r="U24" s="1">
-        <v>1</v>
-      </c>
       <c r="V24" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W24" s="1">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="1">
         <v>44.8</v>
       </c>
-      <c r="X24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
       <c r="E25">
         <v>8</v>
       </c>
@@ -2568,72 +2869,78 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
         <v>3</v>
       </c>
-      <c r="K25" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25">
-        <v>6</v>
-      </c>
-      <c r="N25">
+      <c r="M25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25">
+        <v>6</v>
+      </c>
+      <c r="P25">
         <v>3</v>
       </c>
-      <c r="O25" t="s">
-        <v>27</v>
-      </c>
-      <c r="P25" s="1">
+      <c r="Q25" t="s">
+        <v>29</v>
+      </c>
+      <c r="R25" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q25" s="1">
-        <v>6</v>
-      </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
+        <v>6</v>
+      </c>
+      <c r="T25" s="1">
         <v>1.5</v>
       </c>
-      <c r="S25" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T25" s="1">
-        <v>6</v>
-      </c>
       <c r="U25" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V25" s="1">
+        <v>6</v>
+      </c>
+      <c r="W25" s="1">
         <v>1.5</v>
       </c>
-      <c r="V25" s="1">
-        <v>2</v>
-      </c>
-      <c r="W25" s="1">
+      <c r="X25" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="1">
         <v>30.5</v>
       </c>
-      <c r="X25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
         <v>33</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2642,73 +2949,79 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>2</v>
-      </c>
-      <c r="K26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>29</v>
+      </c>
+      <c r="R26" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="S26" s="1">
+        <v>5</v>
+      </c>
+      <c r="T26" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U26" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V26" s="1">
+        <v>4</v>
+      </c>
+      <c r="W26" s="1">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="1">
         <v>27</v>
       </c>
-      <c r="L26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26">
-        <v>6</v>
-      </c>
-      <c r="N26">
-        <v>2</v>
-      </c>
-      <c r="O26" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>5</v>
-      </c>
-      <c r="R26" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="S26" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T26" s="1">
-        <v>4</v>
-      </c>
-      <c r="U26" s="1">
-        <v>1</v>
-      </c>
-      <c r="V26" s="1">
-        <v>2</v>
-      </c>
-      <c r="W26" s="1">
-        <v>27</v>
-      </c>
-      <c r="X26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
         <v>33</v>
       </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
       <c r="E27">
         <v>8</v>
       </c>
@@ -2716,72 +3029,78 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27">
-        <v>7</v>
-      </c>
-      <c r="N27">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27">
+        <v>7</v>
+      </c>
+      <c r="P27">
         <v>3</v>
       </c>
-      <c r="O27" t="s">
-        <v>27</v>
-      </c>
-      <c r="P27" s="1">
+      <c r="Q27" t="s">
+        <v>29</v>
+      </c>
+      <c r="R27" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q27" s="1">
-        <v>6</v>
-      </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
+        <v>6</v>
+      </c>
+      <c r="T27" s="1">
         <v>1.5</v>
       </c>
-      <c r="S27" s="1">
+      <c r="U27" s="1">
         <v>8.4</v>
       </c>
-      <c r="T27" s="1">
+      <c r="V27" s="1">
         <v>0</v>
       </c>
-      <c r="U27" s="1">
+      <c r="W27" s="1">
         <v>1.5</v>
       </c>
-      <c r="V27" s="1">
-        <v>2</v>
-      </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="1">
         <v>25.7</v>
       </c>
-      <c r="X27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
         <v>33</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -2790,72 +3109,78 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
         <v>3</v>
       </c>
-      <c r="K28" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28">
+      <c r="M28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28">
         <v>10</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>3</v>
       </c>
-      <c r="O28" t="s">
-        <v>27</v>
-      </c>
-      <c r="P28" s="1">
+      <c r="Q28" t="s">
+        <v>29</v>
+      </c>
+      <c r="R28" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="S28" s="1">
         <v>9</v>
       </c>
-      <c r="R28" s="1">
+      <c r="T28" s="1">
         <v>3</v>
       </c>
-      <c r="S28" s="1">
+      <c r="U28" s="1">
         <v>12</v>
       </c>
-      <c r="T28" s="1">
-        <v>6</v>
-      </c>
-      <c r="U28" s="1">
+      <c r="V28" s="1">
+        <v>6</v>
+      </c>
+      <c r="W28" s="1">
         <v>1.5</v>
       </c>
-      <c r="V28" s="1">
-        <v>2</v>
-      </c>
-      <c r="W28" s="1">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="X28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X28" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>39.8</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s">
         <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -2864,146 +3189,158 @@
         <v>8</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
         <v>4</v>
       </c>
-      <c r="K29" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29">
-        <v>7</v>
-      </c>
-      <c r="N29">
-        <v>2</v>
-      </c>
-      <c r="O29" t="s">
-        <v>27</v>
-      </c>
-      <c r="P29" s="1">
+      <c r="M29" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29">
+        <v>7</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>29</v>
+      </c>
+      <c r="R29" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q29" s="1">
-        <v>8</v>
-      </c>
-      <c r="R29" s="1">
+      <c r="S29" s="1">
+        <v>8</v>
+      </c>
+      <c r="T29" s="1">
         <v>1.5</v>
       </c>
-      <c r="S29" s="1">
+      <c r="U29" s="1">
         <v>8.4</v>
       </c>
-      <c r="T29" s="1">
-        <v>8</v>
-      </c>
-      <c r="U29" s="1">
-        <v>1</v>
-      </c>
       <c r="V29" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W29" s="1">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="X29" t="s">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>35.2</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="D30" t="s">
         <v>39</v>
       </c>
-      <c r="C30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30">
+        <v>7</v>
+      </c>
+      <c r="P30">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="S30" s="1">
+        <v>6</v>
+      </c>
+      <c r="T30" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U30" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="V30" s="1">
+        <v>6</v>
+      </c>
+      <c r="W30" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="X30" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>33.7</v>
+      </c>
+      <c r="Z30" t="s">
         <v>37</v>
       </c>
-      <c r="E30">
-        <v>8</v>
-      </c>
-      <c r="F30">
-        <v>6</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>3</v>
-      </c>
-      <c r="K30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30">
-        <v>7</v>
-      </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-      <c r="O30" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>6</v>
-      </c>
-      <c r="R30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="S30" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="T30" s="1">
-        <v>6</v>
-      </c>
-      <c r="U30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="V30" s="1">
-        <v>4</v>
-      </c>
-      <c r="W30" s="1">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="X30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="E31" s="5">
         <v>9</v>
@@ -3011,73 +3348,79 @@
       <c r="F31" s="5">
         <v>8</v>
       </c>
-      <c r="G31" s="5">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5">
-        <v>1</v>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
       </c>
       <c r="I31" s="5">
         <v>1</v>
       </c>
       <c r="J31" s="5">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5">
         <v>5</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="5">
-        <v>7</v>
-      </c>
-      <c r="N31" s="5">
+      <c r="M31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="5">
+        <v>7</v>
+      </c>
+      <c r="P31" s="5">
         <v>3</v>
       </c>
-      <c r="O31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P31" s="7">
+      <c r="Q31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31" s="7">
         <v>6.25</v>
       </c>
-      <c r="Q31" s="7">
-        <v>8</v>
-      </c>
-      <c r="R31" s="7">
+      <c r="S31" s="7">
+        <v>8</v>
+      </c>
+      <c r="T31" s="7">
         <v>3</v>
       </c>
-      <c r="S31" s="7">
+      <c r="U31" s="7">
         <v>8.4</v>
       </c>
-      <c r="T31" s="7">
+      <c r="V31" s="7">
         <v>10</v>
       </c>
-      <c r="U31" s="7">
+      <c r="W31" s="7">
         <v>1.5</v>
       </c>
-      <c r="V31" s="7">
-        <v>2</v>
-      </c>
-      <c r="W31" s="7">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="X31" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="X31" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="7">
+        <v>39.2</v>
+      </c>
+      <c r="Z31" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -3086,72 +3429,78 @@
         <v>9</v>
       </c>
       <c r="G32">
+        <v>9</v>
+      </c>
+      <c r="H32">
         <v>0</v>
       </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
       <c r="I32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
       <c r="M32">
+        <v>8</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
         <v>11</v>
       </c>
-      <c r="N32">
-        <v>2</v>
-      </c>
-      <c r="O32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P32" s="1">
+      <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R32" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="S32" s="1">
         <v>9</v>
       </c>
-      <c r="R32" s="1">
+      <c r="T32" s="1">
         <v>4.5</v>
       </c>
-      <c r="S32" s="1">
+      <c r="U32" s="1">
         <v>13.2</v>
       </c>
-      <c r="T32" s="1">
+      <c r="V32" s="1">
         <v>21</v>
       </c>
-      <c r="U32" s="1">
-        <v>1</v>
-      </c>
-      <c r="V32" s="1">
-        <v>1</v>
-      </c>
       <c r="W32" s="1">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="1">
         <v>56</v>
       </c>
-      <c r="X32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3160,7 +3509,7 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -3168,64 +3517,70 @@
       <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" t="s">
-        <v>27</v>
+      <c r="J33">
+        <v>1</v>
       </c>
       <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33">
         <v>5</v>
       </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <v>6</v>
-      </c>
       <c r="N33">
-        <v>2</v>
-      </c>
-      <c r="O33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>6</v>
+      </c>
+      <c r="P33">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>29</v>
+      </c>
+      <c r="R33" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q33" s="1">
-        <v>6</v>
-      </c>
-      <c r="R33" s="1">
+      <c r="S33" s="1">
+        <v>6</v>
+      </c>
+      <c r="T33" s="1">
         <v>3</v>
       </c>
-      <c r="S33" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T33" s="1">
+      <c r="U33" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V33" s="1">
         <v>13</v>
       </c>
-      <c r="U33" s="1">
-        <v>1</v>
-      </c>
-      <c r="V33" s="1">
+      <c r="W33" s="1">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1">
         <v>4</v>
       </c>
-      <c r="W33" s="1">
+      <c r="Y33" s="1">
         <v>40.5</v>
       </c>
-      <c r="X33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s">
         <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>31</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3234,7 +3589,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -3246,135 +3601,147 @@
         <v>1</v>
       </c>
       <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
         <v>4</v>
       </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>7</v>
-      </c>
       <c r="N34">
-        <v>2</v>
-      </c>
-      <c r="O34" t="s">
-        <v>27</v>
-      </c>
-      <c r="P34" s="1">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>7</v>
+      </c>
+      <c r="P34">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="S34" s="1">
         <v>5</v>
       </c>
-      <c r="R34" s="1">
+      <c r="T34" s="1">
         <v>3</v>
       </c>
-      <c r="S34" s="1">
+      <c r="U34" s="1">
         <v>8.4</v>
       </c>
-      <c r="T34" s="1">
+      <c r="V34" s="1">
         <v>13</v>
       </c>
-      <c r="U34" s="1">
-        <v>1</v>
-      </c>
-      <c r="V34" s="1">
-        <v>2</v>
-      </c>
       <c r="W34" s="1">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="X34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="X34" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>38.7</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35">
+        <v>7</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>8</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>9</v>
+      </c>
+      <c r="P35">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>29</v>
+      </c>
+      <c r="R35" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="S35" s="1">
+        <v>7</v>
+      </c>
+      <c r="T35" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="U35" s="1">
+        <v>10.799999999999999</v>
+      </c>
+      <c r="V35" s="1">
+        <v>21</v>
+      </c>
+      <c r="W35" s="1">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>51.6</v>
+      </c>
+      <c r="Z35" t="s">
         <v>40</v>
       </c>
-      <c r="E35">
-        <v>7</v>
-      </c>
-      <c r="F35">
-        <v>7</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>8</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>9</v>
-      </c>
-      <c r="N35">
-        <v>2</v>
-      </c>
-      <c r="O35" t="s">
-        <v>27</v>
-      </c>
-      <c r="P35" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>7</v>
-      </c>
-      <c r="R35" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="S35" s="1">
-        <v>10.799999999999999</v>
-      </c>
-      <c r="T35" s="1">
-        <v>21</v>
-      </c>
-      <c r="U35" s="1">
-        <v>1</v>
-      </c>
-      <c r="V35" s="1">
-        <v>1</v>
-      </c>
-      <c r="W35" s="1">
-        <v>51.6</v>
-      </c>
-      <c r="X35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s">
         <v>33</v>
       </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
       <c r="E36">
         <v>7</v>
       </c>
@@ -3382,73 +3749,79 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36" t="s">
-        <v>27</v>
+      <c r="J36">
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>6</v>
-      </c>
-      <c r="L36">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>29</v>
       </c>
       <c r="M36">
         <v>6</v>
       </c>
       <c r="N36">
-        <v>2</v>
-      </c>
-      <c r="O36" t="s">
-        <v>27</v>
-      </c>
-      <c r="P36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>29</v>
+      </c>
+      <c r="R36" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q36" s="1">
-        <v>6</v>
-      </c>
-      <c r="R36" s="1">
+      <c r="S36" s="1">
+        <v>6</v>
+      </c>
+      <c r="T36" s="1">
         <v>3</v>
       </c>
-      <c r="S36" s="1">
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="T36" s="1">
+      <c r="U36" s="1">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="V36" s="1">
         <v>15</v>
       </c>
-      <c r="U36" s="1">
-        <v>1</v>
-      </c>
-      <c r="V36" s="1">
-        <v>2</v>
-      </c>
       <c r="W36" s="1">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="1">
         <v>40.5</v>
       </c>
-      <c r="X36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
         <v>33</v>
       </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
       <c r="E37">
         <v>8</v>
       </c>
@@ -3456,72 +3829,78 @@
         <v>7</v>
       </c>
       <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
       </c>
       <c r="I37">
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K37">
-        <v>6</v>
-      </c>
-      <c r="L37">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>29</v>
       </c>
       <c r="M37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>2</v>
       </c>
-      <c r="O37" t="s">
-        <v>27</v>
-      </c>
-      <c r="P37" s="1">
+      <c r="O37">
+        <v>8</v>
+      </c>
+      <c r="P37">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>29</v>
+      </c>
+      <c r="R37" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q37" s="1">
-        <v>7</v>
-      </c>
-      <c r="R37" s="1">
+      <c r="S37" s="1">
+        <v>7</v>
+      </c>
+      <c r="T37" s="1">
         <v>3</v>
       </c>
-      <c r="S37" s="1">
+      <c r="U37" s="1">
         <v>9.6</v>
       </c>
-      <c r="T37" s="1">
+      <c r="V37" s="1">
         <v>18</v>
       </c>
-      <c r="U37" s="1">
-        <v>1</v>
-      </c>
-      <c r="V37" s="1">
-        <v>2</v>
-      </c>
       <c r="W37" s="1">
+        <v>1</v>
+      </c>
+      <c r="X37" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y37" s="1">
         <v>46.9</v>
       </c>
-      <c r="X37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -3530,72 +3909,78 @@
         <v>5</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K38">
-        <v>2</v>
-      </c>
-      <c r="L38">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>29</v>
       </c>
       <c r="M38">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N38">
         <v>2</v>
       </c>
-      <c r="O38" t="s">
-        <v>27</v>
-      </c>
-      <c r="P38" s="1">
+      <c r="O38">
+        <v>8</v>
+      </c>
+      <c r="P38">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R38" s="1">
         <v>4</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="S38" s="1">
         <v>5</v>
       </c>
-      <c r="R38" s="1">
+      <c r="T38" s="1">
         <v>3</v>
       </c>
-      <c r="S38" s="1">
+      <c r="U38" s="1">
         <v>9.6</v>
       </c>
-      <c r="T38" s="1">
+      <c r="V38" s="1">
         <v>10</v>
       </c>
-      <c r="U38" s="1">
-        <v>1</v>
-      </c>
-      <c r="V38" s="1">
-        <v>2</v>
-      </c>
       <c r="W38" s="1">
+        <v>1</v>
+      </c>
+      <c r="X38" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y38" s="1">
         <v>34.6</v>
       </c>
-      <c r="X38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -3604,73 +3989,79 @@
         <v>5</v>
       </c>
       <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
-      <c r="J39">
-        <v>1</v>
+      <c r="J39" t="s">
+        <v>29</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N39">
         <v>2</v>
       </c>
-      <c r="O39" t="s">
-        <v>27</v>
-      </c>
-      <c r="P39" s="1">
+      <c r="O39">
+        <v>8</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>29</v>
+      </c>
+      <c r="R39" s="1">
         <v>4</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="S39" s="1">
         <v>5</v>
       </c>
-      <c r="R39" s="1">
+      <c r="T39" s="1">
         <v>3</v>
       </c>
-      <c r="S39" s="1">
+      <c r="U39" s="1">
         <v>9.6</v>
       </c>
-      <c r="T39" s="1">
+      <c r="V39" s="1">
         <v>10</v>
       </c>
-      <c r="U39" s="1">
-        <v>1</v>
-      </c>
-      <c r="V39" s="1">
+      <c r="W39" s="1">
+        <v>1</v>
+      </c>
+      <c r="X39" s="1">
         <v>4</v>
       </c>
-      <c r="W39" s="1">
+      <c r="Y39" s="1">
         <v>36.6</v>
       </c>
-      <c r="X39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
         <v>33</v>
       </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
       <c r="E40">
         <v>8</v>
       </c>
@@ -3678,147 +4069,159 @@
         <v>7</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40">
         <v>4</v>
       </c>
-      <c r="L40">
-        <v>2</v>
-      </c>
-      <c r="M40">
-        <v>8</v>
-      </c>
       <c r="N40">
         <v>2</v>
       </c>
-      <c r="O40" t="s">
-        <v>27</v>
-      </c>
-      <c r="P40" s="1">
+      <c r="O40">
+        <v>8</v>
+      </c>
+      <c r="P40">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>29</v>
+      </c>
+      <c r="R40" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q40" s="1">
-        <v>7</v>
-      </c>
-      <c r="R40" s="1">
+      <c r="S40" s="1">
+        <v>7</v>
+      </c>
+      <c r="T40" s="1">
         <v>3</v>
       </c>
-      <c r="S40" s="1">
+      <c r="U40" s="1">
         <v>9.6</v>
       </c>
-      <c r="T40" s="1">
+      <c r="V40" s="1">
         <v>14</v>
       </c>
-      <c r="U40" s="1">
-        <v>1</v>
-      </c>
-      <c r="V40" s="1">
-        <v>2</v>
-      </c>
       <c r="W40" s="1">
+        <v>1</v>
+      </c>
+      <c r="X40" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y40" s="1">
         <v>42.9</v>
       </c>
-      <c r="X40" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="E41" s="5">
         <v>7</v>
       </c>
       <c r="F41" s="5">
         <v>6</v>
       </c>
-      <c r="G41" s="5">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>27</v>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
       </c>
       <c r="I41" s="5">
         <v>1</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K41" s="5">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="5">
         <v>5</v>
       </c>
-      <c r="L41" s="5">
-        <v>1</v>
-      </c>
-      <c r="M41" s="5">
-        <v>8</v>
-      </c>
       <c r="N41" s="5">
-        <v>2</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P41" s="7">
+        <v>1</v>
+      </c>
+      <c r="O41" s="5">
+        <v>8</v>
+      </c>
+      <c r="P41" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R41" s="7">
         <v>6.25</v>
       </c>
-      <c r="Q41" s="7">
-        <v>6</v>
-      </c>
-      <c r="R41" s="7">
+      <c r="S41" s="7">
+        <v>6</v>
+      </c>
+      <c r="T41" s="7">
         <v>3</v>
       </c>
-      <c r="S41" s="7">
+      <c r="U41" s="7">
         <v>9.6</v>
       </c>
-      <c r="T41" s="7">
+      <c r="V41" s="7">
         <v>13</v>
       </c>
-      <c r="U41" s="7">
-        <v>1</v>
-      </c>
-      <c r="V41" s="7">
-        <v>2</v>
-      </c>
       <c r="W41" s="7">
+        <v>1</v>
+      </c>
+      <c r="X41" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y41" s="7">
         <v>40.9</v>
       </c>
-      <c r="X41" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z41" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="D42" t="s">
-        <v>31</v>
-      </c>
       <c r="E42">
         <v>8</v>
       </c>
@@ -3826,7 +4229,7 @@
         <v>7</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -3834,64 +4237,70 @@
       <c r="I42">
         <v>1</v>
       </c>
-      <c r="J42" t="s">
-        <v>27</v>
+      <c r="J42">
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>7</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>29</v>
       </c>
       <c r="M42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>2</v>
-      </c>
-      <c r="O42" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42" s="1">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <v>8</v>
+      </c>
+      <c r="P42">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>29</v>
+      </c>
+      <c r="R42" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q42" s="1">
-        <v>7</v>
-      </c>
-      <c r="R42" s="1">
+      <c r="S42" s="1">
+        <v>7</v>
+      </c>
+      <c r="T42" s="1">
         <v>3</v>
       </c>
-      <c r="S42" s="1">
+      <c r="U42" s="1">
         <v>9.6</v>
       </c>
-      <c r="T42" s="1">
+      <c r="V42" s="1">
         <v>17</v>
       </c>
-      <c r="U42" s="1">
-        <v>1</v>
-      </c>
-      <c r="V42" s="1">
-        <v>2</v>
-      </c>
       <c r="W42" s="1">
+        <v>1</v>
+      </c>
+      <c r="X42" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y42" s="1">
         <v>45.9</v>
       </c>
-      <c r="X42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
         <v>33</v>
-      </c>
-      <c r="D43" t="s">
-        <v>31</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -3900,72 +4309,78 @@
         <v>5</v>
       </c>
       <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
       </c>
       <c r="I43">
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M43">
         <v>10</v>
       </c>
-      <c r="L43" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43">
-        <v>7</v>
-      </c>
-      <c r="N43">
-        <v>2</v>
-      </c>
-      <c r="O43" t="s">
-        <v>27</v>
-      </c>
-      <c r="P43" s="1">
+      <c r="N43" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43">
+        <v>7</v>
+      </c>
+      <c r="P43">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>29</v>
+      </c>
+      <c r="R43" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="S43" s="1">
         <v>5</v>
       </c>
-      <c r="R43" s="1">
+      <c r="T43" s="1">
         <v>3</v>
       </c>
-      <c r="S43" s="1">
+      <c r="U43" s="1">
         <v>8.4</v>
       </c>
-      <c r="T43" s="1">
+      <c r="V43" s="1">
         <v>20</v>
       </c>
-      <c r="U43" s="1">
-        <v>1</v>
-      </c>
-      <c r="V43" s="1">
-        <v>2</v>
-      </c>
       <c r="W43" s="1">
+        <v>1</v>
+      </c>
+      <c r="X43" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y43" s="1">
         <v>45.7</v>
       </c>
-      <c r="X43" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
         <v>42</v>
-      </c>
-      <c r="C44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" t="s">
-        <v>40</v>
       </c>
       <c r="E44">
         <v>9</v>
@@ -3974,72 +4389,78 @@
         <v>9</v>
       </c>
       <c r="G44">
+        <v>9</v>
+      </c>
+      <c r="H44">
         <v>0</v>
       </c>
-      <c r="H44" t="s">
-        <v>27</v>
-      </c>
       <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
       </c>
       <c r="L44">
-        <v>2</v>
-      </c>
-      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>29</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="O44">
         <v>9</v>
       </c>
-      <c r="N44">
-        <v>2</v>
-      </c>
-      <c r="O44" t="s">
-        <v>27</v>
-      </c>
-      <c r="P44" s="1">
+      <c r="P44">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>29</v>
+      </c>
+      <c r="R44" s="1">
         <v>4</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="S44" s="1">
         <v>9</v>
       </c>
-      <c r="R44" s="1">
+      <c r="T44" s="1">
         <v>4.5</v>
       </c>
-      <c r="S44" s="1">
+      <c r="U44" s="1">
         <v>10.799999999999999</v>
       </c>
-      <c r="T44" s="1">
-        <v>8</v>
-      </c>
-      <c r="U44" s="1">
-        <v>1</v>
-      </c>
       <c r="V44" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W44" s="1">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="X44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="X44" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>38.3</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
         <v>33</v>
-      </c>
-      <c r="D45" t="s">
-        <v>31</v>
       </c>
       <c r="E45">
         <v>9</v>
@@ -4048,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -4056,64 +4477,70 @@
       <c r="I45">
         <v>1</v>
       </c>
-      <c r="J45" t="s">
-        <v>27</v>
+      <c r="J45">
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>6</v>
-      </c>
-      <c r="L45">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>29</v>
       </c>
       <c r="M45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>2</v>
-      </c>
-      <c r="O45" t="s">
-        <v>27</v>
-      </c>
-      <c r="P45" s="1">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <v>7</v>
+      </c>
+      <c r="P45">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>29</v>
+      </c>
+      <c r="R45" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q45" s="1">
-        <v>8</v>
-      </c>
-      <c r="R45" s="1">
+      <c r="S45" s="1">
+        <v>8</v>
+      </c>
+      <c r="T45" s="1">
         <v>3</v>
       </c>
-      <c r="S45" s="1">
+      <c r="U45" s="1">
         <v>8.4</v>
       </c>
-      <c r="T45" s="1">
+      <c r="V45" s="1">
         <v>15</v>
       </c>
-      <c r="U45" s="1">
-        <v>1</v>
-      </c>
-      <c r="V45" s="1">
-        <v>2</v>
-      </c>
       <c r="W45" s="1">
+        <v>1</v>
+      </c>
+      <c r="X45" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="1">
         <v>43.7</v>
       </c>
-      <c r="X45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E46">
         <v>8</v>
@@ -4122,72 +4549,78 @@
         <v>7</v>
       </c>
       <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="H46">
+        <v>2</v>
       </c>
       <c r="I46">
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M46">
-        <v>8</v>
-      </c>
-      <c r="N46">
-        <v>2</v>
-      </c>
-      <c r="O46" t="s">
-        <v>27</v>
-      </c>
-      <c r="P46" s="1">
+        <v>6</v>
+      </c>
+      <c r="N46" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46">
+        <v>8</v>
+      </c>
+      <c r="P46">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>29</v>
+      </c>
+      <c r="R46" s="1">
         <v>6.25</v>
       </c>
-      <c r="Q46" s="1">
-        <v>7</v>
-      </c>
-      <c r="R46" s="1">
+      <c r="S46" s="1">
+        <v>7</v>
+      </c>
+      <c r="T46" s="1">
         <v>3</v>
       </c>
-      <c r="S46" s="1">
+      <c r="U46" s="1">
         <v>9.6</v>
       </c>
-      <c r="T46" s="1">
+      <c r="V46" s="1">
         <v>12</v>
       </c>
-      <c r="U46" s="1">
-        <v>1</v>
-      </c>
-      <c r="V46" s="1">
+      <c r="W46" s="1">
+        <v>1</v>
+      </c>
+      <c r="X46" s="1">
         <v>4</v>
       </c>
-      <c r="W46" s="1">
+      <c r="Y46" s="1">
         <v>42.9</v>
       </c>
-      <c r="X46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z46" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E47">
         <v>2</v>
@@ -4196,72 +4629,78 @@
         <v>2</v>
       </c>
       <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
-      <c r="H47" t="s">
-        <v>27</v>
-      </c>
       <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>29</v>
       </c>
       <c r="K47">
-        <v>7</v>
-      </c>
-      <c r="L47" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
       </c>
       <c r="M47">
+        <v>7</v>
+      </c>
+      <c r="N47" t="s">
+        <v>29</v>
+      </c>
+      <c r="O47">
         <v>4</v>
       </c>
-      <c r="N47">
-        <v>2</v>
-      </c>
-      <c r="O47" t="s">
-        <v>27</v>
-      </c>
-      <c r="P47" s="1">
+      <c r="P47">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>29</v>
+      </c>
+      <c r="R47" s="1">
         <v>4</v>
       </c>
-      <c r="Q47" s="1">
-        <v>2</v>
-      </c>
-      <c r="R47" s="1">
+      <c r="S47" s="1">
+        <v>2</v>
+      </c>
+      <c r="T47" s="1">
         <v>4.5</v>
       </c>
-      <c r="S47" s="1">
+      <c r="U47" s="1">
         <v>4.8</v>
       </c>
-      <c r="T47" s="1">
+      <c r="V47" s="1">
         <v>16</v>
       </c>
-      <c r="U47" s="1">
-        <v>1</v>
-      </c>
-      <c r="V47" s="1">
-        <v>2</v>
-      </c>
       <c r="W47" s="1">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="X47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="X47" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>34.3</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -4270,73 +4709,79 @@
         <v>7</v>
       </c>
       <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48">
         <v>9</v>
       </c>
-      <c r="L48" t="s">
-        <v>27</v>
-      </c>
-      <c r="M48">
-        <v>8</v>
-      </c>
-      <c r="N48">
-        <v>2</v>
-      </c>
-      <c r="O48" t="s">
-        <v>27</v>
-      </c>
-      <c r="P48" s="1">
+      <c r="N48" t="s">
+        <v>29</v>
+      </c>
+      <c r="O48">
+        <v>8</v>
+      </c>
+      <c r="P48">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>29</v>
+      </c>
+      <c r="R48" s="1">
         <v>9</v>
       </c>
-      <c r="Q48" s="1">
-        <v>7</v>
-      </c>
-      <c r="R48" s="1">
+      <c r="S48" s="1">
+        <v>7</v>
+      </c>
+      <c r="T48" s="1">
         <v>3</v>
       </c>
-      <c r="S48" s="1">
+      <c r="U48" s="1">
         <v>9.6</v>
       </c>
-      <c r="T48" s="1">
+      <c r="V48" s="1">
         <v>18</v>
       </c>
-      <c r="U48" s="1">
-        <v>1</v>
-      </c>
-      <c r="V48" s="1">
-        <v>2</v>
-      </c>
       <c r="W48" s="1">
+        <v>1</v>
+      </c>
+      <c r="X48" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="1">
         <v>49.6</v>
       </c>
-      <c r="X48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
         <v>42</v>
       </c>
-      <c r="C49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" t="s">
-        <v>40</v>
-      </c>
       <c r="E49">
         <v>7</v>
       </c>
@@ -4344,72 +4789,78 @@
         <v>7</v>
       </c>
       <c r="G49">
+        <v>7</v>
+      </c>
+      <c r="H49">
         <v>0</v>
       </c>
-      <c r="H49" t="s">
-        <v>27</v>
-      </c>
-      <c r="I49" t="s">
-        <v>27</v>
-      </c>
-      <c r="J49">
-        <v>1</v>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
       </c>
       <c r="K49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>29</v>
+      </c>
+      <c r="N49">
         <v>4</v>
       </c>
-      <c r="M49">
-        <v>8</v>
-      </c>
-      <c r="N49">
-        <v>2</v>
-      </c>
-      <c r="O49" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" s="1">
+      <c r="O49">
+        <v>8</v>
+      </c>
+      <c r="P49">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>29</v>
+      </c>
+      <c r="R49" s="1">
         <v>4</v>
       </c>
-      <c r="Q49" s="1">
-        <v>7</v>
-      </c>
-      <c r="R49" s="1">
+      <c r="S49" s="1">
+        <v>7</v>
+      </c>
+      <c r="T49" s="1">
         <v>4.5</v>
       </c>
-      <c r="S49" s="1">
+      <c r="U49" s="1">
         <v>9.6</v>
       </c>
-      <c r="T49" s="1">
+      <c r="V49" s="1">
         <v>14</v>
       </c>
-      <c r="U49" s="1">
-        <v>1</v>
-      </c>
-      <c r="V49" s="1">
-        <v>1</v>
-      </c>
       <c r="W49" s="1">
+        <v>1</v>
+      </c>
+      <c r="X49" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="1">
         <v>41.1</v>
       </c>
-      <c r="X49" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E50">
         <v>9</v>
@@ -4418,72 +4869,78 @@
         <v>8</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>1</v>
       </c>
-      <c r="J50" t="s">
-        <v>27</v>
+      <c r="J50">
+        <v>1</v>
       </c>
       <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50">
         <v>9</v>
       </c>
-      <c r="L50" t="s">
-        <v>27</v>
-      </c>
-      <c r="M50">
-        <v>8</v>
-      </c>
-      <c r="N50">
-        <v>2</v>
-      </c>
-      <c r="O50" t="s">
-        <v>27</v>
-      </c>
-      <c r="P50" s="1">
+      <c r="N50" t="s">
+        <v>29</v>
+      </c>
+      <c r="O50">
+        <v>8</v>
+      </c>
+      <c r="P50">
+        <v>2</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>29</v>
+      </c>
+      <c r="R50" s="1">
         <v>9</v>
       </c>
-      <c r="Q50" s="1">
-        <v>8</v>
-      </c>
-      <c r="R50" s="1">
+      <c r="S50" s="1">
+        <v>8</v>
+      </c>
+      <c r="T50" s="1">
         <v>3</v>
       </c>
-      <c r="S50" s="1">
+      <c r="U50" s="1">
         <v>9.6</v>
       </c>
-      <c r="T50" s="1">
+      <c r="V50" s="1">
         <v>18</v>
       </c>
-      <c r="U50" s="1">
-        <v>1</v>
-      </c>
-      <c r="V50" s="1">
-        <v>2</v>
-      </c>
       <c r="W50" s="1">
+        <v>1</v>
+      </c>
+      <c r="X50" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y50" s="1">
         <v>50.6</v>
       </c>
-      <c r="X50" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E51" s="5">
         <v>8</v>
@@ -4491,63 +4948,69 @@
       <c r="F51" s="5">
         <v>8</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51" s="5">
         <v>0</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J51" s="5">
+      <c r="J51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" s="5">
         <v>4</v>
       </c>
-      <c r="K51" s="5">
-        <v>6</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="M51" s="5">
+        <v>6</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O51" s="5">
         <v>11</v>
       </c>
-      <c r="N51" s="5">
-        <v>2</v>
-      </c>
-      <c r="O51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P51" s="7">
+      <c r="P51" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R51" s="7">
         <v>9</v>
       </c>
-      <c r="Q51" s="7">
-        <v>8</v>
-      </c>
-      <c r="R51" s="7">
+      <c r="S51" s="7">
+        <v>8</v>
+      </c>
+      <c r="T51" s="7">
         <v>4.5</v>
       </c>
-      <c r="S51" s="7">
+      <c r="U51" s="7">
         <v>13.2</v>
       </c>
-      <c r="T51" s="7">
+      <c r="V51" s="7">
         <v>20</v>
       </c>
-      <c r="U51" s="7">
-        <v>1</v>
-      </c>
-      <c r="V51" s="7">
+      <c r="W51" s="7">
+        <v>1</v>
+      </c>
+      <c r="X51" s="7">
         <v>4</v>
       </c>
-      <c r="W51" s="7">
+      <c r="Y51" s="7">
         <v>59.7</v>
       </c>
-      <c r="X51" s="5" t="s">
-        <v>38</v>
+      <c r="Z51" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X51" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:X51"/>
   <conditionalFormatting sqref="P2:P51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -4645,125 +5108,2410 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34" style="5" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="16" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="43.5" customHeight="1" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="B7" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="43.5" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="17" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>14</v>
-      </c>
       <c r="B10" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="17" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="17" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="43.5" customHeight="1" spans="1:2" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M74"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="13" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>11</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4">
+        <v>61</v>
+      </c>
+      <c r="M4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>33</v>
+      </c>
+      <c r="K5">
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>94</v>
+      </c>
+      <c r="M5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>127</v>
+      </c>
+      <c r="M6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>38</v>
+      </c>
+      <c r="K7">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>165</v>
+      </c>
+      <c r="M7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>42</v>
+      </c>
+      <c r="K8">
+        <v>21</v>
+      </c>
+      <c r="L8">
+        <v>207</v>
+      </c>
+      <c r="M8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>22</v>
+      </c>
+      <c r="L9">
+        <v>248</v>
+      </c>
+      <c r="M9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>23</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10">
+        <v>44</v>
+      </c>
+      <c r="K10">
+        <v>23</v>
+      </c>
+      <c r="L10">
+        <v>292</v>
+      </c>
+      <c r="M10">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>24</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11">
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>24</v>
+      </c>
+      <c r="L11">
+        <v>337</v>
+      </c>
+      <c r="M11">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12">
+        <v>92</v>
+      </c>
+      <c r="K12">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>429</v>
+      </c>
+      <c r="M12">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13">
+        <v>43</v>
+      </c>
+      <c r="K13">
+        <v>26</v>
+      </c>
+      <c r="L13">
+        <v>472</v>
+      </c>
+      <c r="M13">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>26</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14">
+        <v>43</v>
+      </c>
+      <c r="K14">
+        <v>26</v>
+      </c>
+      <c r="L14">
+        <v>515</v>
+      </c>
+      <c r="M14">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>27</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15">
+        <v>44</v>
+      </c>
+      <c r="K15">
+        <v>27</v>
+      </c>
+      <c r="L15">
+        <v>559</v>
+      </c>
+      <c r="M15">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16">
+        <v>45</v>
+      </c>
+      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="L16">
+        <v>604</v>
+      </c>
+      <c r="M16">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17">
+        <v>45</v>
+      </c>
+      <c r="K17">
+        <v>28</v>
+      </c>
+      <c r="L17">
+        <v>649</v>
+      </c>
+      <c r="M17">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>29</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18">
+        <v>46</v>
+      </c>
+      <c r="K18">
+        <v>29</v>
+      </c>
+      <c r="L18">
+        <v>695</v>
+      </c>
+      <c r="M18">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19">
+        <v>46</v>
+      </c>
+      <c r="K19">
+        <v>29</v>
+      </c>
+      <c r="L19">
+        <v>741</v>
+      </c>
+      <c r="M19">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20">
+        <v>45</v>
+      </c>
+      <c r="K20">
+        <v>30</v>
+      </c>
+      <c r="L20">
+        <v>786</v>
+      </c>
+      <c r="M20">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>30</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21">
+        <v>47</v>
+      </c>
+      <c r="K21">
+        <v>30</v>
+      </c>
+      <c r="L21">
+        <v>833</v>
+      </c>
+      <c r="M21">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>31</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22">
+        <v>112</v>
+      </c>
+      <c r="K22">
+        <v>62</v>
+      </c>
+      <c r="L22">
+        <v>945</v>
+      </c>
+      <c r="M22">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>31</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23">
+        <v>50</v>
+      </c>
+      <c r="K23">
+        <v>31</v>
+      </c>
+      <c r="L23">
+        <v>995</v>
+      </c>
+      <c r="M23">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>11</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>32</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24">
+        <v>47</v>
+      </c>
+      <c r="K24">
+        <v>32</v>
+      </c>
+      <c r="L24">
+        <v>1042</v>
+      </c>
+      <c r="M24">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <v>32</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25">
+        <v>59</v>
+      </c>
+      <c r="K25">
+        <v>32</v>
+      </c>
+      <c r="L25">
+        <v>1101</v>
+      </c>
+      <c r="M25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>33</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>15</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26">
+        <v>52</v>
+      </c>
+      <c r="K26">
+        <v>33</v>
+      </c>
+      <c r="L26">
+        <v>1153</v>
+      </c>
+      <c r="M26">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>33</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27">
+        <v>54</v>
+      </c>
+      <c r="K27">
+        <v>33</v>
+      </c>
+      <c r="L27">
+        <v>1207</v>
+      </c>
+      <c r="M27">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>33</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28">
+        <v>54</v>
+      </c>
+      <c r="K28">
+        <v>33</v>
+      </c>
+      <c r="L28">
+        <v>1261</v>
+      </c>
+      <c r="M28">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <v>34</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29">
+        <v>59</v>
+      </c>
+      <c r="K29">
+        <v>34</v>
+      </c>
+      <c r="L29">
+        <v>1320</v>
+      </c>
+      <c r="M29">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>34</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30">
+        <v>57</v>
+      </c>
+      <c r="K30">
+        <v>34</v>
+      </c>
+      <c r="L30">
+        <v>1377</v>
+      </c>
+      <c r="M30">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>34</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31">
+        <v>53</v>
+      </c>
+      <c r="K31">
+        <v>34</v>
+      </c>
+      <c r="L31">
+        <v>1430</v>
+      </c>
+      <c r="M31">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>35</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32">
+        <v>104</v>
+      </c>
+      <c r="K32">
+        <v>70</v>
+      </c>
+      <c r="L32">
+        <v>1534</v>
+      </c>
+      <c r="M32">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>35</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33">
+        <v>50</v>
+      </c>
+      <c r="K33">
+        <v>35</v>
+      </c>
+      <c r="L33">
+        <v>1584</v>
+      </c>
+      <c r="M33">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>35</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34">
+        <v>54</v>
+      </c>
+      <c r="K34">
+        <v>35</v>
+      </c>
+      <c r="L34">
+        <v>1638</v>
+      </c>
+      <c r="M34">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>36</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35">
+        <v>55</v>
+      </c>
+      <c r="K35">
+        <v>36</v>
+      </c>
+      <c r="L35">
+        <v>1693</v>
+      </c>
+      <c r="M35">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>36</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>15</v>
+      </c>
+      <c r="I36" t="s">
+        <v>29</v>
+      </c>
+      <c r="J36">
+        <v>51</v>
+      </c>
+      <c r="K36">
+        <v>36</v>
+      </c>
+      <c r="L36">
+        <v>1744</v>
+      </c>
+      <c r="M36">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <v>36</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37">
+        <v>57</v>
+      </c>
+      <c r="K37">
+        <v>36</v>
+      </c>
+      <c r="L37">
+        <v>1801</v>
+      </c>
+      <c r="M37">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>36</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38">
+        <v>59</v>
+      </c>
+      <c r="K38">
+        <v>36</v>
+      </c>
+      <c r="L38">
+        <v>1860</v>
+      </c>
+      <c r="M38">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>37</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39">
+        <v>54</v>
+      </c>
+      <c r="K39">
+        <v>37</v>
+      </c>
+      <c r="L39">
+        <v>1914</v>
+      </c>
+      <c r="M39">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>15</v>
+      </c>
+      <c r="I40" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40">
+        <v>56</v>
+      </c>
+      <c r="K40">
+        <v>37</v>
+      </c>
+      <c r="L40">
+        <v>1970</v>
+      </c>
+      <c r="M40">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>37</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s">
+        <v>29</v>
+      </c>
+      <c r="J41">
+        <v>60</v>
+      </c>
+      <c r="K41">
+        <v>37</v>
+      </c>
+      <c r="L41">
+        <v>2030</v>
+      </c>
+      <c r="M41">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>37</v>
+      </c>
+      <c r="G42">
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>72</v>
+      </c>
+      <c r="J42">
+        <v>120</v>
+      </c>
+      <c r="K42">
+        <v>74</v>
+      </c>
+      <c r="L42">
+        <v>2150</v>
+      </c>
+      <c r="M42">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>38</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="H43">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43">
+        <v>57</v>
+      </c>
+      <c r="K43">
+        <v>38</v>
+      </c>
+      <c r="L43">
+        <v>2207</v>
+      </c>
+      <c r="M43">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <v>38</v>
+      </c>
+      <c r="G44">
+        <v>6</v>
+      </c>
+      <c r="H44">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44">
+        <v>59</v>
+      </c>
+      <c r="K44">
+        <v>38</v>
+      </c>
+      <c r="L44">
+        <v>2266</v>
+      </c>
+      <c r="M44">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>38</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>15</v>
+      </c>
+      <c r="I45" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45">
+        <v>53</v>
+      </c>
+      <c r="K45">
+        <v>38</v>
+      </c>
+      <c r="L45">
+        <v>2319</v>
+      </c>
+      <c r="M45">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>38</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46">
+        <v>57</v>
+      </c>
+      <c r="K46">
+        <v>38</v>
+      </c>
+      <c r="L46">
+        <v>2376</v>
+      </c>
+      <c r="M46">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47">
+        <v>39</v>
+      </c>
+      <c r="G47">
+        <v>6</v>
+      </c>
+      <c r="H47">
+        <v>15</v>
+      </c>
+      <c r="I47" t="s">
+        <v>29</v>
+      </c>
+      <c r="J47">
+        <v>60</v>
+      </c>
+      <c r="K47">
+        <v>39</v>
+      </c>
+      <c r="L47">
+        <v>2436</v>
+      </c>
+      <c r="M47">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>39</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>15</v>
+      </c>
+      <c r="I48" t="s">
+        <v>29</v>
+      </c>
+      <c r="J48">
+        <v>54</v>
+      </c>
+      <c r="K48">
+        <v>39</v>
+      </c>
+      <c r="L48">
+        <v>2490</v>
+      </c>
+      <c r="M48">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>39</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>15</v>
+      </c>
+      <c r="I49" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49">
+        <v>60</v>
+      </c>
+      <c r="K49">
+        <v>39</v>
+      </c>
+      <c r="L49">
+        <v>2550</v>
+      </c>
+      <c r="M49">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>39</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J50">
+        <v>54</v>
+      </c>
+      <c r="K50">
+        <v>39</v>
+      </c>
+      <c r="L50">
+        <v>2604</v>
+      </c>
+      <c r="M50">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51">
+        <v>39</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51">
+        <v>60</v>
+      </c>
+      <c r="K51">
+        <v>39</v>
+      </c>
+      <c r="L51">
+        <v>2664</v>
+      </c>
+      <c r="M51">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <v>40</v>
+      </c>
+      <c r="G52">
+        <v>8</v>
+      </c>
+      <c r="H52">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J52">
+        <v>126</v>
+      </c>
+      <c r="K52">
+        <v>80</v>
+      </c>
+      <c r="L52">
+        <v>2790</v>
+      </c>
+      <c r="M52">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>93</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>